--- a/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_64994_completo.xlsx
+++ b/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_64994_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R46984fa09a9d448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R68272a4c1d2c43fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,111 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    878.8575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1144.7974</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1737.6128</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    944.3255</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1347.7325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    688.5869</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    561.7464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -534,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    810.4707</x:v>
+        <x:v>    766.4459</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    467.7672</x:v>
+        <x:v>    461.7172</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_64994_completo.xlsx
+++ b/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_64994_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R68272a4c1d2c43fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R35edbc979ded4ccc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,741 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    746.4527</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    605.0334</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    633.0227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    600.4253</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.6943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    739.9738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    628.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    696.5896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    783.5471</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1374.5102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    556.5242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.9053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    605.4745</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    573.7634</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    628.4146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.7381</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    865.9165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1453.5613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    523.5989</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.9053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    609.6414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    678.5617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    652.8295</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    696.7102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.8086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    743.9244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    687.6422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1262.3687</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    706.9704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    667.5750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    739.2298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    955.2325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    766.9730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    531.5510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    597.0284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    749.9947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    896.2976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1823.5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1030.2459</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    895.3527</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    491.7790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    527.5750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    548.3730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    587.1485</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    619.0821</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    702.2628</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.9368</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>22/08/2026</x:t>
         </x:is>
       </x:c>
@@ -279,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1144.7974</x:v>
+        <x:v>   1121.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -360,6 +1095,21 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    515.9406</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -474,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    587.9104</x:v>
+        <x:v>    579.6549</x:v>
       </x:c>
     </x:row>
     <x:row>
